--- a/branches/ci/gh-pages-preview/observations-summary.xlsx
+++ b/branches/ci/gh-pages-preview/observations-summary.xlsx
@@ -110,7 +110,7 @@
     <t>null#null, null#null, null#null, null#eg-cv</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2027.0.0-ballot.rc1 (required)</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2027.0.0-ballot (required)</t>
   </si>
   <si>
     <t>mii-pr-kardio-ekg-annotation</t>
@@ -122,7 +122,7 @@
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-metriken-ekg-annotationen-mdc|2027.0.0-ballot.rc1 (required)</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-metriken-ekg-annotationen-mdc|2027.0.0-ballot (required)</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
